--- a/exports/trend_1d/BIOCON_full_report.xlsx
+++ b/exports/trend_1d/BIOCON_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q79"/>
+  <dimension ref="A1:U79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,19 +557,19 @@
         <v>7.71</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>42129</v>
+        <v>42130</v>
       </c>
       <c r="H2" t="n">
-        <v>74.45</v>
+        <v>70.90000000000001</v>
       </c>
       <c r="I2" t="n">
         <v>72.02737600161643</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K2" t="n">
-        <v>3.84</v>
+        <v>-1.12</v>
       </c>
       <c r="L2" t="n">
         <v>5.93</v>
@@ -555,7 +578,7 @@
         <v>1.02</v>
       </c>
       <c r="N2" t="n">
-        <v>3.48</v>
+        <v>4.77</v>
       </c>
       <c r="O2" t="n">
         <v>1.56</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>72</v>
+        <v>73</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>42033</v>
+      </c>
+      <c r="S2" t="b">
+        <v>1</v>
+      </c>
+      <c r="T2" t="n">
+        <v>5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -591,19 +626,19 @@
         <v>14.18</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>42174</v>
+        <v>42177</v>
       </c>
       <c r="H3" t="n">
-        <v>77.8</v>
+        <v>78.34999999999999</v>
       </c>
       <c r="I3" t="n">
         <v>78.21130052575529</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K3" t="n">
-        <v>-9.73</v>
+        <v>-10.51</v>
       </c>
       <c r="L3" t="n">
         <v>11.85</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>42152</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>2</v>
+      </c>
+      <c r="U3" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>7.91</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>42212</v>
+        <v>42213</v>
       </c>
       <c r="H4" t="n">
-        <v>76.65000000000001</v>
+        <v>75.15000000000001</v>
       </c>
       <c r="I4" t="n">
         <v>75.42345957538251</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.17</v>
+        <v>-4.08</v>
       </c>
       <c r="L4" t="n">
         <v>4.66</v>
@@ -678,7 +725,19 @@
         <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>42180</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>9.640000000000001</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>42338</v>
+        <v>42339</v>
       </c>
       <c r="H5" t="n">
-        <v>76.95</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="I5" t="n">
         <v>77.72082141538682</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="K5" t="n">
-        <v>-2.4</v>
+        <v>-3.66</v>
       </c>
       <c r="L5" t="n">
         <v>7.52</v>
@@ -735,7 +794,19 @@
         <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>84</v>
+        <v>85</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>42215</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>6</v>
+      </c>
+      <c r="U5" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>6.56</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>42384</v>
+        <v>42387</v>
       </c>
       <c r="H6" t="n">
-        <v>83.65000000000001</v>
+        <v>80.25</v>
       </c>
       <c r="I6" t="n">
         <v>83.37099150516451</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="K6" t="n">
-        <v>7.38</v>
+        <v>3.02</v>
       </c>
       <c r="L6" t="n">
         <v>2.25</v>
       </c>
       <c r="M6" t="n">
-        <v>1.71</v>
+        <v>7.35</v>
       </c>
       <c r="N6" t="n">
-        <v>3.07</v>
+        <v>4.06</v>
       </c>
       <c r="O6" t="n">
         <v>1.23</v>
@@ -792,7 +863,19 @@
         <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>42369</v>
+      </c>
+      <c r="S6" t="b">
+        <v>1</v>
+      </c>
+      <c r="T6" t="n">
+        <v>2</v>
+      </c>
+      <c r="U6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -819,19 +902,19 @@
         <v>11.94</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>42461</v>
+        <v>42464</v>
       </c>
       <c r="H7" t="n">
-        <v>81.8</v>
+        <v>82</v>
       </c>
       <c r="I7" t="n">
         <v>81.89216857912203</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.93</v>
+        <v>-2.18</v>
       </c>
       <c r="L7" t="n">
         <v>4.86</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>42397</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>4</v>
+      </c>
+      <c r="U7" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -876,19 +971,19 @@
         <v>7.46</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>42566</v>
+        <v>42569</v>
       </c>
       <c r="H8" t="n">
-        <v>117.35</v>
+        <v>115.7</v>
       </c>
       <c r="I8" t="n">
         <v>115.7723286046379</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="K8" t="n">
-        <v>43.11</v>
+        <v>41.1</v>
       </c>
       <c r="L8" t="n">
         <v>1.1</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>42488</v>
+      </c>
+      <c r="S8" t="b">
+        <v>1</v>
+      </c>
+      <c r="T8" t="n">
+        <v>4</v>
+      </c>
+      <c r="U8" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="9">
@@ -933,28 +1040,28 @@
         <v>9.15</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>42572</v>
+        <v>42573</v>
       </c>
       <c r="H9" t="n">
-        <v>116.75</v>
+        <v>134.95</v>
       </c>
       <c r="I9" t="n">
         <v>125.514555040016</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.91</v>
+        <v>-16.64</v>
       </c>
       <c r="L9" t="n">
-        <v>3.24</v>
+        <v>18.84</v>
       </c>
       <c r="M9" t="n">
-        <v>0.55</v>
+        <v>2.61</v>
       </c>
       <c r="N9" t="n">
-        <v>1.54</v>
+        <v>15.59</v>
       </c>
       <c r="O9" t="n">
         <v>-1.41</v>
@@ -963,7 +1070,19 @@
         <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S9" t="b">
+        <v>0</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>15.99</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>42668</v>
+        <v>42669</v>
       </c>
       <c r="H10" t="n">
-        <v>156.6</v>
+        <v>151.2</v>
       </c>
       <c r="I10" t="n">
         <v>151.9600593716062</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K10" t="n">
-        <v>16.04</v>
+        <v>12.04</v>
       </c>
       <c r="L10" t="n">
         <v>12.19</v>
@@ -1020,7 +1139,19 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>63</v>
+        <v>64</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>42579</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>4</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,22 +1178,22 @@
         <v>11.87</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>42712</v>
+        <v>42713</v>
       </c>
       <c r="H11" t="n">
-        <v>154.05</v>
+        <v>157.25</v>
       </c>
       <c r="I11" t="n">
         <v>156.6736059016837</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.88</v>
+        <v>-4</v>
       </c>
       <c r="L11" t="n">
-        <v>3.41</v>
+        <v>4.63</v>
       </c>
       <c r="M11" t="n">
         <v>2.09</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>42670</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>3</v>
+      </c>
+      <c r="U11" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="12">
@@ -1104,28 +1247,28 @@
         <v>8.130000000000001</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>42727</v>
+        <v>42730</v>
       </c>
       <c r="H12" t="n">
-        <v>155.1</v>
+        <v>149.05</v>
       </c>
       <c r="I12" t="n">
         <v>149.7369998800687</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.37</v>
+        <v>-5.21</v>
       </c>
       <c r="L12" t="n">
-        <v>3.08</v>
+        <v>5.63</v>
       </c>
       <c r="M12" t="n">
         <v>0.91</v>
       </c>
       <c r="N12" t="n">
-        <v>1.72</v>
+        <v>3.9</v>
       </c>
       <c r="O12" t="n">
         <v>2.08</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S12" t="b">
+        <v>0</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1161,28 +1316,28 @@
         <v>10.09</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>42741</v>
+        <v>42744</v>
       </c>
       <c r="H13" t="n">
-        <v>159.9</v>
+        <v>168.9</v>
       </c>
       <c r="I13" t="n">
         <v>163.9858982717364</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="K13" t="n">
-        <v>-7.28</v>
+        <v>-13.32</v>
       </c>
       <c r="L13" t="n">
-        <v>8.52</v>
+        <v>13.96</v>
       </c>
       <c r="M13" t="n">
-        <v>0.6</v>
+        <v>0.66</v>
       </c>
       <c r="N13" t="n">
-        <v>2.52</v>
+        <v>5.63</v>
       </c>
       <c r="O13" t="n">
         <v>-3.9</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>42733</v>
+      </c>
+      <c r="S13" t="b">
+        <v>1</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,19 +1385,19 @@
         <v>10.22</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>42795</v>
+        <v>42796</v>
       </c>
       <c r="H14" t="n">
-        <v>185.7</v>
+        <v>172.15</v>
       </c>
       <c r="I14" t="n">
         <v>174.0133746640898</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K14" t="n">
-        <v>9.949999999999999</v>
+        <v>1.92</v>
       </c>
       <c r="L14" t="n">
         <v>5.24</v>
@@ -1239,7 +1406,7 @@
         <v>0.88</v>
       </c>
       <c r="N14" t="n">
-        <v>1.96</v>
+        <v>7.3</v>
       </c>
       <c r="O14" t="n">
         <v>5.63</v>
@@ -1248,7 +1415,19 @@
         <v>1</v>
       </c>
       <c r="Q14" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>42760</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="15">
@@ -1275,28 +1454,28 @@
         <v>14.05</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>42849</v>
+        <v>42850</v>
       </c>
       <c r="H15" t="n">
-        <v>177.6</v>
+        <v>194.25</v>
       </c>
       <c r="I15" t="n">
         <v>192.3971125742686</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="K15" t="n">
-        <v>-3.17</v>
+        <v>-12.84</v>
       </c>
       <c r="L15" t="n">
-        <v>12.58</v>
+        <v>15.02</v>
       </c>
       <c r="M15" t="n">
-        <v>2.43</v>
+        <v>3.89</v>
       </c>
       <c r="N15" t="n">
-        <v>3.78</v>
+        <v>9.380000000000001</v>
       </c>
       <c r="O15" t="n">
         <v>-7.3</v>
@@ -1305,7 +1484,19 @@
         <v>1</v>
       </c>
       <c r="Q15" t="n">
-        <v>35</v>
+        <v>36</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>42824</v>
+      </c>
+      <c r="S15" t="b">
+        <v>1</v>
+      </c>
+      <c r="T15" t="n">
+        <v>2</v>
+      </c>
+      <c r="U15" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>10.91</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>42857</v>
+        <v>42858</v>
       </c>
       <c r="H16" t="n">
-        <v>181.15</v>
+        <v>172.1</v>
       </c>
       <c r="I16" t="n">
         <v>173.0500986831583</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K16" t="n">
-        <v>-6.74</v>
+        <v>-11.4</v>
       </c>
       <c r="L16" t="n">
-        <v>7.1</v>
+        <v>12.74</v>
       </c>
       <c r="M16" t="n">
         <v>1.82</v>
       </c>
       <c r="N16" t="n">
-        <v>3.29</v>
+        <v>5</v>
       </c>
       <c r="O16" t="n">
         <v>9.380000000000001</v>
@@ -1362,7 +1553,19 @@
         <v>1</v>
       </c>
       <c r="Q16" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>42852</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,25 +1592,25 @@
         <v>14.03</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>42895</v>
+        <v>42898</v>
       </c>
       <c r="H17" t="n">
-        <v>170.45</v>
+        <v>172.6</v>
       </c>
       <c r="I17" t="n">
         <v>171.7275029243299</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="K17" t="n">
-        <v>0.96</v>
+        <v>-0.29</v>
       </c>
       <c r="L17" t="n">
         <v>5.08</v>
       </c>
       <c r="M17" t="n">
-        <v>1.23</v>
+        <v>1.7</v>
       </c>
       <c r="N17" t="n">
         <v>4.6</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>42880</v>
+      </c>
+      <c r="S17" t="b">
+        <v>1</v>
+      </c>
+      <c r="T17" t="n">
+        <v>2</v>
+      </c>
+      <c r="U17" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>8.07</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>42950</v>
+        <v>42951</v>
       </c>
       <c r="H18" t="n">
-        <v>187.4</v>
+        <v>178.5</v>
       </c>
       <c r="I18" t="n">
         <v>184.6022580041857</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K18" t="n">
-        <v>8.57</v>
+        <v>3.42</v>
       </c>
       <c r="L18" t="n">
         <v>8.4</v>
@@ -1467,7 +1682,7 @@
         <v>6.84</v>
       </c>
       <c r="N18" t="n">
-        <v>4.39</v>
+        <v>4.75</v>
       </c>
       <c r="O18" t="n">
         <v>1.26</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>42915</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>3</v>
+      </c>
+      <c r="U18" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="19">
@@ -1503,28 +1730,28 @@
         <v>12.88</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>43017</v>
+        <v>43018</v>
       </c>
       <c r="H19" t="n">
-        <v>172.1</v>
+        <v>184.55</v>
       </c>
       <c r="I19" t="n">
         <v>181.8424527595614</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="K19" t="n">
-        <v>3.59</v>
+        <v>-3.39</v>
       </c>
       <c r="L19" t="n">
-        <v>3.59</v>
+        <v>4.09</v>
       </c>
       <c r="M19" t="n">
         <v>3.76</v>
       </c>
       <c r="N19" t="n">
-        <v>2.84</v>
+        <v>7.23</v>
       </c>
       <c r="O19" t="n">
         <v>-4.75</v>
@@ -1533,7 +1760,19 @@
         <v>1</v>
       </c>
       <c r="Q19" t="n">
-        <v>44</v>
+        <v>45</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>42978</v>
+      </c>
+      <c r="S19" t="b">
+        <v>1</v>
+      </c>
+      <c r="T19" t="n">
+        <v>3</v>
+      </c>
+      <c r="U19" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>12.41</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>43255</v>
+        <v>43256</v>
       </c>
       <c r="H20" t="n">
-        <v>327.25</v>
+        <v>303.7</v>
       </c>
       <c r="I20" t="n">
         <v>308.6819483315498</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="K20" t="n">
-        <v>77.31999999999999</v>
+        <v>64.56</v>
       </c>
       <c r="L20" t="n">
         <v>6.94</v>
@@ -1581,7 +1820,7 @@
         <v>7.44</v>
       </c>
       <c r="N20" t="n">
-        <v>5.56</v>
+        <v>7.2</v>
       </c>
       <c r="O20" t="n">
         <v>7.23</v>
@@ -1590,7 +1829,19 @@
         <v>1</v>
       </c>
       <c r="Q20" t="n">
-        <v>161</v>
+        <v>162</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>43034</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>9</v>
+      </c>
+      <c r="U20" t="n">
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>19.81</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>43333</v>
+        <v>43335</v>
       </c>
       <c r="H21" t="n">
-        <v>306.15</v>
+        <v>306.4</v>
       </c>
       <c r="I21" t="n">
         <v>306.3223994040416</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.89</v>
       </c>
       <c r="L21" t="n">
         <v>14.69</v>
@@ -1647,7 +1898,19 @@
         <v>1</v>
       </c>
       <c r="Q21" t="n">
-        <v>55</v>
+        <v>56</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>43279</v>
+      </c>
+      <c r="S21" t="b">
+        <v>1</v>
+      </c>
+      <c r="T21" t="n">
+        <v>3</v>
+      </c>
+      <c r="U21" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="22">
@@ -1674,25 +1937,25 @@
         <v>7.98</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>43377</v>
+        <v>43378</v>
       </c>
       <c r="H22" t="n">
-        <v>312.3</v>
+        <v>305.95</v>
       </c>
       <c r="I22" t="n">
         <v>309.9277542176229</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K22" t="n">
-        <v>1.93</v>
+        <v>-0.15</v>
       </c>
       <c r="L22" t="n">
         <v>3.85</v>
       </c>
       <c r="M22" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="N22" t="n">
         <v>5.49</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>43342</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>3</v>
+      </c>
+      <c r="U22" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>16.42</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>43483</v>
+        <v>43486</v>
       </c>
       <c r="H23" t="n">
-        <v>326</v>
+        <v>331.5</v>
       </c>
       <c r="I23" t="n">
         <v>329.1259862078006</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K23" t="n">
-        <v>-6.55</v>
+        <v>-8.35</v>
       </c>
       <c r="L23" t="n">
         <v>11.73</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>43398</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>4</v>
+      </c>
+      <c r="U23" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>6.33</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>43510</v>
+        <v>43511</v>
       </c>
       <c r="H24" t="n">
-        <v>320.9</v>
+        <v>307.6</v>
       </c>
       <c r="I24" t="n">
         <v>315.612521021791</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="K24" t="n">
-        <v>-3.2</v>
+        <v>-7.21</v>
       </c>
       <c r="L24" t="n">
-        <v>5.26</v>
+        <v>7.87</v>
       </c>
       <c r="M24" t="n">
         <v>1.13</v>
       </c>
       <c r="N24" t="n">
-        <v>2.36</v>
+        <v>4.14</v>
       </c>
       <c r="O24" t="n">
         <v>1.69</v>
@@ -1818,7 +2105,19 @@
         <v>0</v>
       </c>
       <c r="Q24" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>43496</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>2</v>
+      </c>
+      <c r="U24" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="25">
@@ -1845,19 +2144,19 @@
         <v>10.19</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>43662</v>
+        <v>43663</v>
       </c>
       <c r="H25" t="n">
-        <v>258.15</v>
+        <v>262.9</v>
       </c>
       <c r="I25" t="n">
         <v>259.6196395676665</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="K25" t="n">
-        <v>16.08</v>
+        <v>14.53</v>
       </c>
       <c r="L25" t="n">
         <v>4.36</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>101</v>
+        <v>102</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>43524</v>
+      </c>
+      <c r="S25" t="b">
+        <v>1</v>
+      </c>
+      <c r="T25" t="n">
+        <v>6</v>
+      </c>
+      <c r="U25" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>8.48</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>43664</v>
+        <v>43665</v>
       </c>
       <c r="H26" t="n">
-        <v>263.05</v>
+        <v>240.3</v>
       </c>
       <c r="I26" t="n">
         <v>242.796161347851</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.06</v>
+        <v>-8.6</v>
       </c>
       <c r="L26" t="n">
-        <v>1.48</v>
+        <v>9.470000000000001</v>
       </c>
       <c r="M26" t="n">
         <v>0</v>
       </c>
       <c r="N26" t="n">
-        <v>0</v>
+        <v>8.65</v>
       </c>
       <c r="O26" t="n">
         <v>1.84</v>
@@ -1932,7 +2243,19 @@
         <v>0</v>
       </c>
       <c r="Q26" t="n">
-        <v>2</v>
+        <v>3</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S26" t="b">
+        <v>0</v>
+      </c>
+      <c r="T26" t="n">
+        <v>1</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="27">
@@ -1959,19 +2282,19 @@
         <v>15.5</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>43747</v>
+        <v>43748</v>
       </c>
       <c r="H27" t="n">
-        <v>233.5</v>
+        <v>240.15</v>
       </c>
       <c r="I27" t="n">
         <v>238.7868089103791</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K27" t="n">
-        <v>2.83</v>
+        <v>0.06</v>
       </c>
       <c r="L27" t="n">
         <v>10.15</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>53</v>
+        <v>54</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>43671</v>
+      </c>
+      <c r="S27" t="b">
+        <v>1</v>
+      </c>
+      <c r="T27" t="n">
+        <v>4</v>
+      </c>
+      <c r="U27" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>11.26</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>43889</v>
+        <v>43892</v>
       </c>
       <c r="H28" t="n">
-        <v>286.9</v>
+        <v>282.65</v>
       </c>
       <c r="I28" t="n">
         <v>282.7930488655603</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K28" t="n">
-        <v>19.47</v>
+        <v>17.7</v>
       </c>
       <c r="L28" t="n">
         <v>2.98</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>99</v>
+        <v>100</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>43769</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>6</v>
+      </c>
+      <c r="U28" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>14.62</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>43924</v>
+        <v>43928</v>
       </c>
       <c r="H29" t="n">
-        <v>290.95</v>
+        <v>318.3</v>
       </c>
       <c r="I29" t="n">
         <v>309.8572233421717</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K29" t="n">
-        <v>-2.94</v>
+        <v>-12.61</v>
       </c>
       <c r="L29" t="n">
-        <v>11.09</v>
+        <v>13.21</v>
       </c>
       <c r="M29" t="n">
-        <v>2.74</v>
+        <v>3.11</v>
       </c>
       <c r="N29" t="n">
-        <v>8.539999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O29" t="n">
         <v>-1.48</v>
@@ -2103,7 +2450,19 @@
         <v>0</v>
       </c>
       <c r="Q29" t="n">
-        <v>23</v>
+        <v>24</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>43916</v>
+      </c>
+      <c r="S29" t="b">
+        <v>1</v>
+      </c>
+      <c r="T29" t="n">
+        <v>2</v>
+      </c>
+      <c r="U29" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="30">
@@ -2130,19 +2489,19 @@
         <v>20.95</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>44067</v>
+        <v>44068</v>
       </c>
       <c r="H30" t="n">
-        <v>392.2</v>
+        <v>387.4</v>
       </c>
       <c r="I30" t="n">
         <v>389.3237679114951</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="K30" t="n">
-        <v>23.22</v>
+        <v>21.71</v>
       </c>
       <c r="L30" t="n">
         <v>6.6</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>96</v>
+        <v>97</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>43951</v>
+      </c>
+      <c r="S30" t="b">
+        <v>1</v>
+      </c>
+      <c r="T30" t="n">
+        <v>5</v>
+      </c>
+      <c r="U30" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="31">
@@ -2187,22 +2558,22 @@
         <v>8.449999999999999</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>44076</v>
+        <v>44077</v>
       </c>
       <c r="H31" t="n">
-        <v>411.25</v>
+        <v>425.35</v>
       </c>
       <c r="I31" t="n">
         <v>417.3279340393139</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K31" t="n">
-        <v>-6.16</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="L31" t="n">
-        <v>6.71</v>
+        <v>10.09</v>
       </c>
       <c r="M31" t="n">
         <v>1.67</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>44070</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>2</v>
+      </c>
+      <c r="U31" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="32">
@@ -2244,22 +2627,22 @@
         <v>10.8</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>44097</v>
+        <v>44098</v>
       </c>
       <c r="H32" t="n">
-        <v>423.9</v>
+        <v>408.25</v>
       </c>
       <c r="I32" t="n">
         <v>409.4597310377554</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K32" t="n">
-        <v>-0.34</v>
+        <v>-4.02</v>
       </c>
       <c r="L32" t="n">
-        <v>3.68</v>
+        <v>4.53</v>
       </c>
       <c r="M32" t="n">
         <v>1.39</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>44098</v>
+      </c>
+      <c r="S32" t="b">
+        <v>0</v>
+      </c>
+      <c r="T32" t="n">
+        <v>1</v>
+      </c>
+      <c r="U32" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="33">
@@ -2301,22 +2696,22 @@
         <v>13.28</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>44111</v>
+        <v>44112</v>
       </c>
       <c r="H33" t="n">
-        <v>452.15</v>
+        <v>469.15</v>
       </c>
       <c r="I33" t="n">
         <v>462.4622079661287</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K33" t="n">
-        <v>-10.75</v>
+        <v>-14.92</v>
       </c>
       <c r="L33" t="n">
-        <v>14.94</v>
+        <v>16.04</v>
       </c>
       <c r="M33" t="n">
         <v>1.57</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S33" t="b">
+        <v>0</v>
+      </c>
+      <c r="T33" t="n">
+        <v>1</v>
+      </c>
+      <c r="U33" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="34">
@@ -2358,22 +2765,22 @@
         <v>11.99</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>44127</v>
+        <v>44130</v>
       </c>
       <c r="H34" t="n">
-        <v>417.2</v>
+        <v>402.55</v>
       </c>
       <c r="I34" t="n">
         <v>412.9111732345927</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K34" t="n">
-        <v>-11.07</v>
+        <v>-14.2</v>
       </c>
       <c r="L34" t="n">
-        <v>11.39</v>
+        <v>16.92</v>
       </c>
       <c r="M34" t="n">
         <v>2.23</v>
@@ -2388,7 +2795,19 @@
         <v>0</v>
       </c>
       <c r="Q34" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,22 +2834,22 @@
         <v>12.89</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>44169</v>
+        <v>44172</v>
       </c>
       <c r="H35" t="n">
-        <v>442.65</v>
+        <v>450.6</v>
       </c>
       <c r="I35" t="n">
         <v>444.5118796588222</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="K35" t="n">
-        <v>-9.960000000000001</v>
+        <v>-11.94</v>
       </c>
       <c r="L35" t="n">
-        <v>10.3</v>
+        <v>12.61</v>
       </c>
       <c r="M35" t="n">
         <v>3.66</v>
@@ -2445,7 +2864,19 @@
         <v>0</v>
       </c>
       <c r="Q35" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>44133</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>3</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,28 +2903,28 @@
         <v>9.550000000000001</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>44217</v>
+        <v>44218</v>
       </c>
       <c r="H36" t="n">
-        <v>441.95</v>
+        <v>393.75</v>
       </c>
       <c r="I36" t="n">
         <v>433.8034456188062</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="K36" t="n">
-        <v>-1.92</v>
+        <v>-12.62</v>
       </c>
       <c r="L36" t="n">
-        <v>3.02</v>
+        <v>16.49</v>
       </c>
       <c r="M36" t="n">
-        <v>2.71</v>
+        <v>4.42</v>
       </c>
       <c r="N36" t="n">
-        <v>4.65</v>
+        <v>10.91</v>
       </c>
       <c r="O36" t="n">
         <v>1.8</v>
@@ -2502,7 +2933,19 @@
         <v>0</v>
       </c>
       <c r="Q36" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>44196</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,19 +2972,19 @@
         <v>14.83</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>44294</v>
+        <v>44295</v>
       </c>
       <c r="H37" t="n">
-        <v>413.25</v>
+        <v>420.3</v>
       </c>
       <c r="I37" t="n">
         <v>418.5056737440185</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K37" t="n">
-        <v>-4.95</v>
+        <v>-6.74</v>
       </c>
       <c r="L37" t="n">
         <v>7.87</v>
@@ -2559,7 +3002,19 @@
         <v>1</v>
       </c>
       <c r="Q37" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>44224</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>4</v>
+      </c>
+      <c r="U37" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>6.83</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>44313</v>
+        <v>44314</v>
       </c>
       <c r="H38" t="n">
-        <v>398.1</v>
+        <v>390.85</v>
       </c>
       <c r="I38" t="n">
         <v>391.5805929163306</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K38" t="n">
-        <v>-5.28</v>
+        <v>-7.01</v>
       </c>
       <c r="L38" t="n">
-        <v>6.69</v>
+        <v>7.8</v>
       </c>
       <c r="M38" t="n">
         <v>0.4</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>8.41</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>44354</v>
+        <v>44355</v>
       </c>
       <c r="H39" t="n">
-        <v>389.05</v>
+        <v>402.45</v>
       </c>
       <c r="I39" t="n">
         <v>402.2651128650928</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K39" t="n">
-        <v>0.46</v>
+        <v>-2.97</v>
       </c>
       <c r="L39" t="n">
-        <v>2.92</v>
+        <v>3.17</v>
       </c>
       <c r="M39" t="n">
         <v>1.25</v>
       </c>
       <c r="N39" t="n">
-        <v>2.17</v>
+        <v>3.44</v>
       </c>
       <c r="O39" t="n">
         <v>-1.82</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>44315</v>
+      </c>
+      <c r="S39" t="b">
+        <v>1</v>
+      </c>
+      <c r="T39" t="n">
+        <v>3</v>
+      </c>
+      <c r="U39" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>6.77</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>44382</v>
+        <v>44383</v>
       </c>
       <c r="H40" t="n">
-        <v>403.4</v>
+        <v>388.85</v>
       </c>
       <c r="I40" t="n">
         <v>392.2330906116644</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K40" t="n">
-        <v>0.24</v>
+        <v>-3.38</v>
       </c>
       <c r="L40" t="n">
-        <v>3.33</v>
+        <v>3.59</v>
       </c>
       <c r="M40" t="n">
         <v>0.86</v>
       </c>
       <c r="N40" t="n">
-        <v>1.77</v>
+        <v>3.61</v>
       </c>
       <c r="O40" t="n">
         <v>3.44</v>
@@ -2730,7 +3209,19 @@
         <v>0</v>
       </c>
       <c r="Q40" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>44371</v>
+      </c>
+      <c r="S40" t="b">
+        <v>1</v>
+      </c>
+      <c r="T40" t="n">
+        <v>2</v>
+      </c>
+      <c r="U40" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="41">
@@ -2757,22 +3248,22 @@
         <v>8.52</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>44393</v>
+        <v>44396</v>
       </c>
       <c r="H41" t="n">
-        <v>409.3</v>
+        <v>411.4</v>
       </c>
       <c r="I41" t="n">
         <v>409.6115106405381</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K41" t="n">
-        <v>-5.26</v>
+        <v>-5.8</v>
       </c>
       <c r="L41" t="n">
-        <v>6.29</v>
+        <v>6.57</v>
       </c>
       <c r="M41" t="n">
         <v>0.55</v>
@@ -2787,7 +3278,19 @@
         <v>0</v>
       </c>
       <c r="Q41" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S41" t="b">
+        <v>0</v>
+      </c>
+      <c r="T41" t="n">
+        <v>1</v>
+      </c>
+      <c r="U41" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>6.55</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>44403</v>
+        <v>44404</v>
       </c>
       <c r="H42" t="n">
-        <v>389.5</v>
+        <v>379.55</v>
       </c>
       <c r="I42" t="n">
         <v>384.471437868743</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K42" t="n">
-        <v>-5.32</v>
+        <v>-7.74</v>
       </c>
       <c r="L42" t="n">
-        <v>5.86</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="M42" t="n">
         <v>2.73</v>
       </c>
       <c r="N42" t="n">
-        <v>2.17</v>
+        <v>2.55</v>
       </c>
       <c r="O42" t="n">
         <v>0.51</v>
@@ -2844,7 +3347,19 @@
         <v>0</v>
       </c>
       <c r="Q42" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>10.03</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>44497</v>
+        <v>44498</v>
       </c>
       <c r="H43" t="n">
-        <v>337.85</v>
+        <v>351.1</v>
       </c>
       <c r="I43" t="n">
         <v>350.6008957628941</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="K43" t="n">
-        <v>10.99</v>
+        <v>7.5</v>
       </c>
       <c r="L43" t="n">
         <v>6.68</v>
@@ -2901,7 +3416,19 @@
         <v>0</v>
       </c>
       <c r="Q43" t="n">
-        <v>65</v>
+        <v>66</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>44406</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>5</v>
+      </c>
+      <c r="U43" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>10.99</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>44617</v>
+        <v>44620</v>
       </c>
       <c r="H44" t="n">
-        <v>394.55</v>
+        <v>348.85</v>
       </c>
       <c r="I44" t="n">
         <v>371.7947367969737</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="K44" t="n">
-        <v>12.38</v>
+        <v>-0.64</v>
       </c>
       <c r="L44" t="n">
         <v>4.44</v>
@@ -2949,7 +3476,7 @@
         <v>3.03</v>
       </c>
       <c r="N44" t="n">
-        <v>5.39</v>
+        <v>11.58</v>
       </c>
       <c r="O44" t="n">
         <v>3.92</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>83</v>
+        <v>84</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>44525</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>5</v>
+      </c>
+      <c r="U44" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="45">
@@ -2985,19 +3524,19 @@
         <v>20.4</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>44671</v>
+        <v>44672</v>
       </c>
       <c r="H45" t="n">
-        <v>352.55</v>
+        <v>373.95</v>
       </c>
       <c r="I45" t="n">
         <v>362.8331898753164</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="K45" t="n">
-        <v>-1.06</v>
+        <v>-7.2</v>
       </c>
       <c r="L45" t="n">
         <v>13.2</v>
@@ -3006,7 +3545,7 @@
         <v>1.84</v>
       </c>
       <c r="N45" t="n">
-        <v>4.32</v>
+        <v>6.07</v>
       </c>
       <c r="O45" t="n">
         <v>-11.58</v>
@@ -3015,7 +3554,19 @@
         <v>1</v>
       </c>
       <c r="Q45" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S45" t="b">
+        <v>1</v>
+      </c>
+      <c r="T45" t="n">
+        <v>2</v>
+      </c>
+      <c r="U45" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="46">
@@ -3042,25 +3593,25 @@
         <v>12.74</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>44687</v>
+        <v>44690</v>
       </c>
       <c r="H46" t="n">
-        <v>348</v>
+        <v>338.55</v>
       </c>
       <c r="I46" t="n">
         <v>345.7536150053174</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K46" t="n">
-        <v>-6.94</v>
+        <v>-9.470000000000001</v>
       </c>
       <c r="L46" t="n">
-        <v>7.18</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="M46" t="n">
-        <v>1.1</v>
+        <v>2.24</v>
       </c>
       <c r="N46" t="n">
         <v>3.89</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,19 +3662,19 @@
         <v>12.47</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>44876</v>
+        <v>44879</v>
       </c>
       <c r="H47" t="n">
-        <v>281.05</v>
+        <v>286</v>
       </c>
       <c r="I47" t="n">
         <v>284.6234667428653</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="K47" t="n">
-        <v>16.98</v>
+        <v>15.52</v>
       </c>
       <c r="L47" t="n">
         <v>3.35</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>129</v>
+        <v>130</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S47" t="b">
+        <v>1</v>
+      </c>
+      <c r="T47" t="n">
+        <v>7</v>
+      </c>
+      <c r="U47" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>8.98</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>44911</v>
+        <v>44914</v>
       </c>
       <c r="H48" t="n">
-        <v>266.1</v>
+        <v>263.05</v>
       </c>
       <c r="I48" t="n">
         <v>265.7668041114501</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K48" t="n">
-        <v>-6.96</v>
+        <v>-8.02</v>
       </c>
       <c r="L48" t="n">
-        <v>7.34</v>
+        <v>8.57</v>
       </c>
       <c r="M48" t="n">
         <v>0.32</v>
@@ -3186,7 +3761,19 @@
         <v>0</v>
       </c>
       <c r="Q48" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>44889</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,19 +3800,19 @@
         <v>7.31</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45027</v>
+        <v>45028</v>
       </c>
       <c r="H49" t="n">
-        <v>216</v>
+        <v>223.65</v>
       </c>
       <c r="I49" t="n">
         <v>222.4948510538199</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="K49" t="n">
-        <v>17.89</v>
+        <v>14.98</v>
       </c>
       <c r="L49" t="n">
         <v>5.3</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>77</v>
+        <v>78</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S49" t="b">
+        <v>1</v>
+      </c>
+      <c r="T49" t="n">
+        <v>5</v>
+      </c>
+      <c r="U49" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>10.74</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45131</v>
+        <v>45132</v>
       </c>
       <c r="H50" t="n">
-        <v>249.5</v>
+        <v>245.7</v>
       </c>
       <c r="I50" t="n">
         <v>249.396657352023</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="K50" t="n">
-        <v>11.56</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="L50" t="n">
         <v>3.31</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>71</v>
+        <v>72</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>4</v>
+      </c>
+      <c r="U50" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="51">
@@ -3327,28 +3938,28 @@
         <v>9.1</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45145</v>
+        <v>45146</v>
       </c>
       <c r="H51" t="n">
-        <v>261.4</v>
+        <v>273.15</v>
       </c>
       <c r="I51" t="n">
         <v>267.5877356113377</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K51" t="n">
-        <v>-6.39</v>
+        <v>-11.17</v>
       </c>
       <c r="L51" t="n">
-        <v>7.57</v>
+        <v>11.52</v>
       </c>
       <c r="M51" t="n">
-        <v>1.02</v>
+        <v>1.07</v>
       </c>
       <c r="N51" t="n">
-        <v>3.1</v>
+        <v>4.5</v>
       </c>
       <c r="O51" t="n">
         <v>-1.52</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45134</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,19 +4007,19 @@
         <v>9.48</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45211</v>
+        <v>45212</v>
       </c>
       <c r="H52" t="n">
-        <v>260.1</v>
+        <v>254.55</v>
       </c>
       <c r="I52" t="n">
         <v>257.158162386259</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="K52" t="n">
-        <v>-4.78</v>
+        <v>-6.81</v>
       </c>
       <c r="L52" t="n">
         <v>8.59</v>
@@ -3414,7 +4037,19 @@
         <v>1</v>
       </c>
       <c r="Q52" t="n">
-        <v>45</v>
+        <v>46</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S52" t="b">
+        <v>1</v>
+      </c>
+      <c r="T52" t="n">
+        <v>3</v>
+      </c>
+      <c r="U52" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>7.44</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45259</v>
+        <v>45260</v>
       </c>
       <c r="H53" t="n">
-        <v>236.75</v>
+        <v>238.3</v>
       </c>
       <c r="I53" t="n">
         <v>237.4473897794551</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K53" t="n">
-        <v>6.99</v>
+        <v>6.38</v>
       </c>
       <c r="L53" t="n">
         <v>1.94</v>
@@ -3471,7 +4106,19 @@
         <v>0</v>
       </c>
       <c r="Q53" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>6.17</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>45315</v>
+        <v>45316</v>
       </c>
       <c r="H54" t="n">
-        <v>264.5</v>
+        <v>258.7</v>
       </c>
       <c r="I54" t="n">
         <v>260.1295389104839</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="K54" t="n">
-        <v>10.99</v>
+        <v>8.56</v>
       </c>
       <c r="L54" t="n">
         <v>0.9</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>39</v>
+        <v>40</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45288</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="55">
@@ -3555,28 +4214,28 @@
         <v>12.3</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>45327</v>
+        <v>45328</v>
       </c>
       <c r="H55" t="n">
-        <v>284.65</v>
+        <v>298.55</v>
       </c>
       <c r="I55" t="n">
         <v>286.4591560194473</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K55" t="n">
-        <v>-10.03</v>
+        <v>-15.4</v>
       </c>
       <c r="L55" t="n">
-        <v>11.91</v>
+        <v>18.71</v>
       </c>
       <c r="M55" t="n">
         <v>1.01</v>
       </c>
       <c r="N55" t="n">
-        <v>3.62</v>
+        <v>4.88</v>
       </c>
       <c r="O55" t="n">
         <v>-2.19</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,28 +4283,28 @@
         <v>11.59</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>45363</v>
+        <v>45364</v>
       </c>
       <c r="H56" t="n">
-        <v>270.35</v>
+        <v>252.85</v>
       </c>
       <c r="I56" t="n">
         <v>263.9599230408689</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="K56" t="n">
-        <v>-9.449999999999999</v>
+        <v>-15.31</v>
       </c>
       <c r="L56" t="n">
-        <v>12.58</v>
+        <v>16.13</v>
       </c>
       <c r="M56" t="n">
         <v>1.48</v>
       </c>
       <c r="N56" t="n">
-        <v>3.97</v>
+        <v>6.47</v>
       </c>
       <c r="O56" t="n">
         <v>4.88</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>45351</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,22 +4352,22 @@
         <v>17.01</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>45405</v>
+        <v>45406</v>
       </c>
       <c r="H57" t="n">
-        <v>280.15</v>
+        <v>289.6</v>
       </c>
       <c r="I57" t="n">
         <v>280.6171250360736</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="K57" t="n">
-        <v>-10.8</v>
+        <v>-14.53</v>
       </c>
       <c r="L57" t="n">
-        <v>12</v>
+        <v>16.67</v>
       </c>
       <c r="M57" t="n">
         <v>3.09</v>
@@ -3699,7 +4382,19 @@
         <v>1</v>
       </c>
       <c r="Q57" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>10.52</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>45491</v>
+        <v>45492</v>
       </c>
       <c r="H58" t="n">
-        <v>343.2</v>
+        <v>335.2</v>
       </c>
       <c r="I58" t="n">
         <v>336.8666313367651</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="K58" t="n">
-        <v>18.51</v>
+        <v>15.75</v>
       </c>
       <c r="L58" t="n">
         <v>6.92</v>
@@ -3756,7 +4451,19 @@
         <v>0</v>
       </c>
       <c r="Q58" t="n">
-        <v>59</v>
+        <v>60</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>45407</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>4</v>
+      </c>
+      <c r="U58" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="59">
@@ -3783,25 +4490,25 @@
         <v>10.53</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>45498</v>
+        <v>45499</v>
       </c>
       <c r="H59" t="n">
-        <v>361.85</v>
+        <v>368.5</v>
       </c>
       <c r="I59" t="n">
         <v>362.8745075940625</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K59" t="n">
-        <v>-7.95</v>
+        <v>-9.93</v>
       </c>
       <c r="L59" t="n">
-        <v>8.56</v>
+        <v>12.41</v>
       </c>
       <c r="M59" t="n">
-        <v>0.89</v>
+        <v>1.15</v>
       </c>
       <c r="N59" t="n">
         <v>3.98</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>45498</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,22 +4559,22 @@
         <v>9.83</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>45517</v>
+        <v>45518</v>
       </c>
       <c r="H60" t="n">
-        <v>337.1</v>
+        <v>327.65</v>
       </c>
       <c r="I60" t="n">
         <v>332.2885589639286</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K60" t="n">
-        <v>-8.52</v>
+        <v>-11.09</v>
       </c>
       <c r="L60" t="n">
-        <v>10.38</v>
+        <v>12.25</v>
       </c>
       <c r="M60" t="n">
         <v>3.38</v>
@@ -3870,7 +4589,19 @@
         <v>0</v>
       </c>
       <c r="Q60" t="n">
-        <v>13</v>
+        <v>14</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S60" t="b">
+        <v>0</v>
+      </c>
+      <c r="T60" t="n">
+        <v>1</v>
+      </c>
+      <c r="U60" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -3897,28 +4628,28 @@
         <v>12.73</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>45538</v>
+        <v>45539</v>
       </c>
       <c r="H61" t="n">
-        <v>361.9</v>
+        <v>379.4</v>
       </c>
       <c r="I61" t="n">
         <v>369.3677738424848</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K61" t="n">
-        <v>-10.45</v>
+        <v>-15.79</v>
       </c>
       <c r="L61" t="n">
-        <v>12.31</v>
+        <v>16.95</v>
       </c>
       <c r="M61" t="n">
         <v>2.48</v>
       </c>
       <c r="N61" t="n">
-        <v>4.06</v>
+        <v>4.84</v>
       </c>
       <c r="O61" t="n">
         <v>-2.8</v>
@@ -3927,7 +4658,19 @@
         <v>0</v>
       </c>
       <c r="Q61" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S61" t="b">
+        <v>1</v>
+      </c>
+      <c r="T61" t="n">
+        <v>2</v>
+      </c>
+      <c r="U61" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>11.6</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>45568</v>
+        <v>45569</v>
       </c>
       <c r="H62" t="n">
-        <v>356.55</v>
+        <v>346.35</v>
       </c>
       <c r="I62" t="n">
         <v>352.6586772221594</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K62" t="n">
-        <v>-6.02</v>
+        <v>-8.710000000000001</v>
       </c>
       <c r="L62" t="n">
-        <v>7.49</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="M62" t="n">
         <v>2.23</v>
@@ -3984,7 +4727,19 @@
         <v>1</v>
       </c>
       <c r="Q62" t="n">
-        <v>21</v>
+        <v>22</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S62" t="b">
+        <v>1</v>
+      </c>
+      <c r="T62" t="n">
+        <v>2</v>
+      </c>
+      <c r="U62" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="63">
@@ -4011,28 +4766,28 @@
         <v>12.73</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>45604</v>
+        <v>45607</v>
       </c>
       <c r="H63" t="n">
-        <v>321.3</v>
+        <v>348.7</v>
       </c>
       <c r="I63" t="n">
         <v>345.838404308196</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K63" t="n">
-        <v>7.23</v>
+        <v>-0.68</v>
       </c>
       <c r="L63" t="n">
         <v>3.98</v>
       </c>
       <c r="M63" t="n">
-        <v>0.83</v>
+        <v>2.4</v>
       </c>
       <c r="N63" t="n">
-        <v>3.77</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="O63" t="n">
         <v>-2.86</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>2</v>
+      </c>
+      <c r="U63" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>13.72</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>45645</v>
+        <v>45646</v>
       </c>
       <c r="H64" t="n">
-        <v>350.35</v>
+        <v>335.95</v>
       </c>
       <c r="I64" t="n">
         <v>345.6603788507128</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="K64" t="n">
-        <v>0.47</v>
+        <v>-3.66</v>
       </c>
       <c r="L64" t="n">
         <v>8.369999999999999</v>
@@ -4098,7 +4865,19 @@
         <v>1</v>
       </c>
       <c r="Q64" t="n">
-        <v>27</v>
+        <v>28</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S64" t="b">
+        <v>1</v>
+      </c>
+      <c r="T64" t="n">
+        <v>2</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4125,22 +4904,22 @@
         <v>11.65</v>
       </c>
       <c r="G65" s="1" t="n">
-        <v>45653</v>
+        <v>45656</v>
       </c>
       <c r="H65" t="n">
-        <v>352.55</v>
+        <v>367.7</v>
       </c>
       <c r="I65" t="n">
         <v>366.1545627217744</v>
       </c>
       <c r="J65" s="2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="K65" t="n">
-        <v>-4.94</v>
+        <v>-9.449999999999999</v>
       </c>
       <c r="L65" t="n">
-        <v>5.34</v>
+        <v>9.82</v>
       </c>
       <c r="M65" t="n">
         <v>0.91</v>
@@ -4155,7 +4934,19 @@
         <v>1</v>
       </c>
       <c r="Q65" t="n">
-        <v>5</v>
+        <v>6</v>
+      </c>
+      <c r="R65" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>2</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="66">
@@ -4182,19 +4973,19 @@
         <v>11.14</v>
       </c>
       <c r="G66" s="1" t="n">
-        <v>45685</v>
+        <v>45686</v>
       </c>
       <c r="H66" t="n">
-        <v>359.9</v>
+        <v>355.7</v>
       </c>
       <c r="I66" t="n">
         <v>356.0444163599225</v>
       </c>
       <c r="J66" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K66" t="n">
-        <v>-2.12</v>
+        <v>-3.26</v>
       </c>
       <c r="L66" t="n">
         <v>4.7</v>
@@ -4212,7 +5003,19 @@
         <v>1</v>
       </c>
       <c r="Q66" t="n">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="R66" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S66" t="b">
+        <v>0</v>
+      </c>
+      <c r="T66" t="n">
+        <v>1</v>
+      </c>
+      <c r="U66" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -4239,19 +5042,19 @@
         <v>14.53</v>
       </c>
       <c r="G67" s="1" t="n">
-        <v>45734</v>
+        <v>45735</v>
       </c>
       <c r="H67" t="n">
-        <v>336.35</v>
+        <v>341.9</v>
       </c>
       <c r="I67" t="n">
         <v>340.1357826300145</v>
       </c>
       <c r="J67" s="2" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="K67" t="n">
-        <v>5.44</v>
+        <v>3.88</v>
       </c>
       <c r="L67" t="n">
         <v>12.34</v>
@@ -4269,7 +5072,19 @@
         <v>0</v>
       </c>
       <c r="Q67" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R67" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S67" t="b">
+        <v>1</v>
+      </c>
+      <c r="T67" t="n">
+        <v>3</v>
+      </c>
+      <c r="U67" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="68">
@@ -4296,28 +5111,28 @@
         <v>10.02</v>
       </c>
       <c r="G68" s="1" t="n">
-        <v>45751</v>
+        <v>45754</v>
       </c>
       <c r="H68" t="n">
-        <v>327.8</v>
+        <v>307.5</v>
       </c>
       <c r="I68" t="n">
         <v>321.8077929155035</v>
       </c>
       <c r="J68" s="2" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="K68" t="n">
-        <v>-4.12</v>
+        <v>-10.06</v>
       </c>
       <c r="L68" t="n">
-        <v>6.03</v>
+        <v>12.55</v>
       </c>
       <c r="M68" t="n">
-        <v>0.9399999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="N68" t="n">
-        <v>5.19</v>
+        <v>6.19</v>
       </c>
       <c r="O68" t="n">
         <v>1.65</v>
@@ -4326,7 +5141,19 @@
         <v>0</v>
       </c>
       <c r="Q68" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R68" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S68" t="b">
+        <v>1</v>
+      </c>
+      <c r="T68" t="n">
+        <v>2</v>
+      </c>
+      <c r="U68" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="69">
@@ -4353,22 +5180,22 @@
         <v>12.06</v>
       </c>
       <c r="G69" s="1" t="n">
-        <v>45783</v>
+        <v>45784</v>
       </c>
       <c r="H69" t="n">
-        <v>341.45</v>
+        <v>346.5</v>
       </c>
       <c r="I69" t="n">
         <v>344.5940162076727</v>
       </c>
       <c r="J69" s="2" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="K69" t="n">
-        <v>-11.04</v>
+        <v>-12.68</v>
       </c>
       <c r="L69" t="n">
-        <v>12.36</v>
+        <v>13.45</v>
       </c>
       <c r="M69" t="n">
         <v>4.47</v>
@@ -4383,7 +5210,19 @@
         <v>1</v>
       </c>
       <c r="Q69" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R69" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S69" t="b">
+        <v>1</v>
+      </c>
+      <c r="T69" t="n">
+        <v>2</v>
+      </c>
+      <c r="U69" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="70">
@@ -4410,19 +5249,19 @@
         <v>11.28</v>
       </c>
       <c r="G70" s="1" t="n">
-        <v>45873</v>
+        <v>45874</v>
       </c>
       <c r="H70" t="n">
-        <v>382.4</v>
+        <v>372.35</v>
       </c>
       <c r="I70" t="n">
         <v>372.6192656607398</v>
       </c>
       <c r="J70" s="2" t="n">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="K70" t="n">
-        <v>10.36</v>
+        <v>7.46</v>
       </c>
       <c r="L70" t="n">
         <v>8.25</v>
@@ -4440,7 +5279,19 @@
         <v>0</v>
       </c>
       <c r="Q70" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R70" s="3" t="n">
+        <v>45806</v>
+      </c>
+      <c r="S70" t="b">
+        <v>1</v>
+      </c>
+      <c r="T70" t="n">
+        <v>4</v>
+      </c>
+      <c r="U70" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="71">
@@ -4467,19 +5318,19 @@
         <v>10.82</v>
       </c>
       <c r="G71" s="1" t="n">
-        <v>45950</v>
+        <v>45951</v>
       </c>
       <c r="H71" t="n">
-        <v>364.3</v>
+        <v>366.1</v>
       </c>
       <c r="I71" t="n">
         <v>365.0756396214446</v>
       </c>
       <c r="J71" s="2" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="K71" t="n">
-        <v>2.16</v>
+        <v>1.68</v>
       </c>
       <c r="L71" t="n">
         <v>3.88</v>
@@ -4497,7 +5348,19 @@
         <v>0</v>
       </c>
       <c r="Q71" t="n">
-        <v>52</v>
+        <v>53</v>
+      </c>
+      <c r="R71" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S71" t="b">
+        <v>1</v>
+      </c>
+      <c r="T71" t="n">
+        <v>3</v>
+      </c>
+      <c r="U71" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="72">
@@ -4524,19 +5387,19 @@
         <v>6.59</v>
       </c>
       <c r="G72" s="1" t="n">
-        <v>45994</v>
+        <v>45995</v>
       </c>
       <c r="H72" t="n">
-        <v>410</v>
+        <v>388.35</v>
       </c>
       <c r="I72" t="n">
         <v>388.445774281264</v>
       </c>
       <c r="J72" s="2" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K72" t="n">
-        <v>11.99</v>
+        <v>6.08</v>
       </c>
       <c r="L72" t="n">
         <v>2.25</v>
@@ -4545,7 +5408,7 @@
         <v>0.63</v>
       </c>
       <c r="N72" t="n">
-        <v>3.65</v>
+        <v>5.28</v>
       </c>
       <c r="O72" t="n">
         <v>0.49</v>
@@ -4554,7 +5417,19 @@
         <v>0</v>
       </c>
       <c r="Q72" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R72" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S72" t="b">
+        <v>1</v>
+      </c>
+      <c r="T72" t="n">
+        <v>3</v>
+      </c>
+      <c r="U72" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="73">
@@ -4581,19 +5456,19 @@
         <v>11.44</v>
       </c>
       <c r="G73" s="1" t="n">
-        <v>46077</v>
+        <v>46078</v>
       </c>
       <c r="H73" t="n">
-        <v>390.75</v>
+        <v>395.85</v>
       </c>
       <c r="I73" t="n">
         <v>393.9022795872879</v>
       </c>
       <c r="J73" s="2" t="n">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K73" t="n">
-        <v>-0.62</v>
+        <v>-1.93</v>
       </c>
       <c r="L73" t="n">
         <v>6.03</v>
@@ -4611,7 +5486,19 @@
         <v>1</v>
       </c>
       <c r="Q73" t="n">
-        <v>57</v>
+        <v>58</v>
+      </c>
+      <c r="R73" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S73" t="b">
+        <v>1</v>
+      </c>
+      <c r="T73" t="n">
+        <v>4</v>
+      </c>
+      <c r="U73" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="74">
@@ -4638,28 +5525,28 @@
         <v>7.24</v>
       </c>
       <c r="G74" s="1" t="n">
-        <v>46099</v>
+        <v>46100</v>
       </c>
       <c r="H74" t="n">
-        <v>382.6</v>
+        <v>368.55</v>
       </c>
       <c r="I74" t="n">
         <v>370.2832127790829</v>
       </c>
       <c r="J74" s="2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="K74" t="n">
-        <v>-3.35</v>
+        <v>-6.9</v>
       </c>
       <c r="L74" t="n">
-        <v>6.76</v>
+        <v>7.48</v>
       </c>
       <c r="M74" t="n">
         <v>2.51</v>
       </c>
       <c r="N74" t="n">
-        <v>2.47</v>
+        <v>3.67</v>
       </c>
       <c r="O74" t="n">
         <v>1.31</v>
@@ -4668,7 +5555,19 @@
         <v>0</v>
       </c>
       <c r="Q74" t="n">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="R74" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S74" t="b">
+        <v>0</v>
+      </c>
+      <c r="T74" t="n">
+        <v>1</v>
+      </c>
+      <c r="U74" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -4695,22 +5594,22 @@
         <v>10.21</v>
       </c>
       <c r="G75" s="1" t="n">
-        <v>46147</v>
+        <v>46148</v>
       </c>
       <c r="H75" t="n">
-        <v>368.25</v>
+        <v>380.6</v>
       </c>
       <c r="I75" t="n">
         <v>378.5421892827741</v>
       </c>
       <c r="J75" s="2" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="K75" t="n">
-        <v>0.08</v>
+        <v>-3.27</v>
       </c>
       <c r="L75" t="n">
-        <v>3.83</v>
+        <v>4.33</v>
       </c>
       <c r="M75" t="n">
         <v>3.41</v>
@@ -4725,7 +5624,19 @@
         <v>0</v>
       </c>
       <c r="Q75" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R75" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S75" t="b">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>3</v>
+      </c>
+      <c r="U75" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="76">
@@ -4752,19 +5663,19 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G76" s="1" t="n">
-        <v>46210</v>
+        <v>46211</v>
       </c>
       <c r="H76" t="n">
-        <v>406.9</v>
+        <v>397.05</v>
       </c>
       <c r="I76" t="n">
         <v>401.8424833576227</v>
       </c>
       <c r="J76" s="2" t="n">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="K76" t="n">
-        <v>6.91</v>
+        <v>4.32</v>
       </c>
       <c r="L76" t="n">
         <v>2.51</v>
@@ -4782,7 +5693,19 @@
         <v>0</v>
       </c>
       <c r="Q76" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R76" s="3" t="n">
+        <v>46168</v>
+      </c>
+      <c r="S76" t="b">
+        <v>1</v>
+      </c>
+      <c r="T76" t="n">
+        <v>3</v>
+      </c>
+      <c r="U76" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="77">
@@ -4809,22 +5732,22 @@
         <v>10.37</v>
       </c>
       <c r="G77" s="1" t="n">
-        <v>46218</v>
+        <v>46219</v>
       </c>
       <c r="H77" t="n">
-        <v>434.6</v>
+        <v>440.7</v>
       </c>
       <c r="I77" t="n">
         <v>438.2036334036788</v>
       </c>
       <c r="J77" s="2" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="K77" t="n">
-        <v>-9.460000000000001</v>
+        <v>-10.99</v>
       </c>
       <c r="L77" t="n">
-        <v>11.95</v>
+        <v>12.62</v>
       </c>
       <c r="M77" t="n">
         <v>3.99</v>
@@ -4839,7 +5762,19 @@
         <v>0</v>
       </c>
       <c r="Q77" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R77" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S77" t="b">
+        <v>0</v>
+      </c>
+      <c r="T77" t="n">
+        <v>1</v>
+      </c>
+      <c r="U77" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -4866,28 +5801,28 @@
         <v>9.73</v>
       </c>
       <c r="G78" s="1" t="n">
-        <v>46265</v>
+        <v>46266</v>
       </c>
       <c r="H78" t="n">
-        <v>412</v>
+        <v>401.05</v>
       </c>
       <c r="I78" t="n">
         <v>401.7506822908314</v>
       </c>
       <c r="J78" s="2" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K78" t="n">
-        <v>-6.51</v>
+        <v>-9</v>
       </c>
       <c r="L78" t="n">
-        <v>8.859999999999999</v>
+        <v>9.16</v>
       </c>
       <c r="M78" t="n">
         <v>1.51</v>
       </c>
       <c r="N78" t="n">
-        <v>2.35</v>
+        <v>2.66</v>
       </c>
       <c r="O78" t="n">
         <v>1.4</v>
@@ -4896,7 +5831,19 @@
         <v>0</v>
       </c>
       <c r="Q78" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R78" s="3" t="n">
+        <v>46231</v>
+      </c>
+      <c r="S78" t="b">
+        <v>1</v>
+      </c>
+      <c r="T78" t="n">
+        <v>3</v>
+      </c>
+      <c r="U78" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="79">
@@ -4947,6 +5894,14 @@
       <c r="Q79" t="n">
         <v>39</v>
       </c>
+      <c r="R79" s="3" t="n">
+        <v>46294</v>
+      </c>
+      <c r="S79" t="b">
+        <v>1</v>
+      </c>
+      <c r="T79" t="inlineStr"/>
+      <c r="U79" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -9905,7 +10860,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>53.6</v>
+        <v>55.2</v>
       </c>
     </row>
     <row r="6">
@@ -9915,7 +10870,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -9925,7 +10880,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>237</v>
+        <v>238</v>
       </c>
     </row>
     <row r="8">
@@ -9935,7 +10890,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -9945,7 +10900,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="10">
@@ -9955,7 +10910,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>111.2</v>
+        <v>112.2</v>
       </c>
     </row>
     <row r="11">
@@ -9995,7 +10950,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.85</v>
+        <v>-1.97</v>
       </c>
     </row>
     <row r="15">
@@ -10005,7 +10960,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5.08</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="16">
@@ -10015,7 +10970,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>-1.47</v>
+        <v>-4.98</v>
       </c>
     </row>
     <row r="17">
@@ -10025,7 +10980,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>77.31999999999999</v>
+        <v>64.56</v>
       </c>
     </row>
     <row r="18">
@@ -10035,7 +10990,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>42.9</v>
+        <v>28.6</v>
       </c>
     </row>
     <row r="19">
@@ -10045,7 +11000,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>6.91</v>
+        <v>8.550000000000001</v>
       </c>
     </row>
     <row r="20">
@@ -10055,7 +11010,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>6.68</v>
+        <v>7.87</v>
       </c>
     </row>
     <row r="21">
@@ -10065,7 +11020,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.94</v>
+        <v>18.84</v>
       </c>
     </row>
     <row r="22">
@@ -10075,7 +11030,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>50</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
@@ -10085,7 +11040,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>19</v>
+        <v>27</v>
       </c>
     </row>
     <row r="24">
@@ -10095,7 +11050,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>2.1</v>
+        <v>2.39</v>
       </c>
     </row>
     <row r="25">
@@ -10105,7 +11060,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7.44</v>
+        <v>8.76</v>
       </c>
     </row>
     <row r="26">
@@ -10115,7 +11070,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.99</v>
+        <v>5.09</v>
       </c>
     </row>
     <row r="27">
@@ -10125,7 +11080,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>8.539999999999999</v>
+        <v>15.59</v>
       </c>
     </row>
     <row r="28">
@@ -10135,7 +11090,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>36</v>
+        <v>51</v>
       </c>
     </row>
     <row r="29">
